--- a/resources/print-on-demand/files/pod-adv-allocation.xlsx
+++ b/resources/print-on-demand/files/pod-adv-allocation.xlsx
@@ -19,12 +19,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="£#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;×&quot;"/>
     <numFmt numFmtId="166" formatCode="0&quot;%&quot;"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,11 +65,6 @@
       <color rgb="000C2733"/>
       <sz val="12"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="005A5A5A"/>
-    </font>
-    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -96,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,8 +118,6 @@
     <xf numFmtId="167" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -490,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -511,15 +504,14 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Unit contribution £ (before burdens — from the sum)</t>
+          <t>Unit contribution $ (before burdens — from the sum)</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9.23</v>
+        <v>9.210000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -562,7 +554,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -585,7 +576,6 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
@@ -596,11 +586,10 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>may be negative — a real loss. Anchor: hoodie 9.23 → 5.06 / 2.66.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>may be negative — a real loss. Anchor: hoodie 9.21 → 5.04 / 2.64.</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
@@ -614,10 +603,6 @@
           <t>ePORTS — your ecom source. eports.global.</t>
         </is>
       </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="13" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -651,21 +636,20 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Loaded PRE-AD contribution £</t>
+          <t>Loaded PRE-AD contribution $</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>22.83</v>
+        <v>22.81</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Profit I require per sale £</t>
+          <t>Profit I require per sale $</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
@@ -675,14 +659,13 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Sale price (revenue) £ — for ROAS</t>
+          <t>Sale price (revenue) $ — for ROAS</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
         <v>68</v>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -711,11 +694,10 @@
         <v/>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Anchor: premium 22.83 − 12 = 10.83 ceiling, 68/22.83 ≈ 3.0× break-even.</t>
+          <t>Anchor: premium 22.81 − 12 = 10.81 ceiling, 68/22.81 ≈ 3.0× break-even.</t>
         </is>
       </c>
     </row>
@@ -726,7 +708,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
@@ -737,7 +718,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Price £</t>
+          <t>Price $</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
@@ -747,11 +728,11 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Loaded contribution £</t>
+          <t>Loaded contribution $</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>22.83</v>
+        <v>22.81</v>
       </c>
     </row>
     <row r="18">
@@ -774,7 +755,6 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
@@ -808,15 +788,13 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Anchor: 15% off £68 = £10.20 sticker, but only £8.87 true hit (fee falls).</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
+          <t>Anchor: 15% off $68 = $10.20 sticker, but only $8.87 true hit (fee falls).</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
@@ -863,15 +841,14 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Loaded £ per sale</t>
+          <t>Loaded $ per sale</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>22.83</v>
+        <v>22.81</v>
       </c>
     </row>
     <row r="5">
@@ -894,7 +871,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -917,7 +893,6 @@
         <v/>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
@@ -928,11 +903,10 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>out-rank a fat one that eats your week. Anchor: 22.83 × 13 / 5 ≈ 297 / 59.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+          <t>out-rank a fat one that eats your week. Anchor: 22.81 × 13 / 5 ≈ 297 / 59.</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>

--- a/resources/print-on-demand/files/pod-adv-allocation.xlsx
+++ b/resources/print-on-demand/files/pod-adv-allocation.xlsx
@@ -600,7 +600,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
